--- a/model/lodestone_model.xlsx
+++ b/model/lodestone_model.xlsx
@@ -18,7 +18,9 @@
     <sheet name="Tucuma" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Xavantina" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Corporate_NAV" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Sources" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Comps" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Precedents" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sources" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="Caraiba_AISC_LOM" vbProcedure="false">Caraiba!$C$66</definedName>
@@ -48,6 +50,26 @@
     <definedName function="false" hidden="false" name="CG_PNAV" vbProcedure="false">Corporate_NAV!$C$22</definedName>
     <definedName function="false" hidden="false" name="CG_PRICE_CAD" vbProcedure="false">Corporate_NAV!$C$21</definedName>
     <definedName function="false" hidden="false" name="CG_SHARES" vbProcedure="false">Corporate_NAV!$C$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EVLB_MEAN" vbProcedure="false">Comps!$M$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EVLB_MED" vbProcedure="false">Comps!$M$19</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EVLB_Q1" vbProcedure="false">Comps!$M$20</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EVLB_Q3" vbProcedure="false">Comps!$M$21</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EV_EBITDA_MEAN" vbProcedure="false">Comps!$H$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EV_EBITDA_MED" vbProcedure="false">Comps!$H$19</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EV_EBITDA_Q1" vbProcedure="false">Comps!$H$20</definedName>
+    <definedName function="false" hidden="false" name="COMPS_EV_EBITDA_Q3" vbProcedure="false">Comps!$H$21</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PCF_MEAN" vbProcedure="false">Comps!$I$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PCF_MED" vbProcedure="false">Comps!$I$19</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PCF_Q1" vbProcedure="false">Comps!$I$20</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PCF_Q3" vbProcedure="false">Comps!$I$21</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PNAV_MEAN" vbProcedure="false">Comps!$J$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PNAV_MED" vbProcedure="false">Comps!$J$19</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PNAV_Q1" vbProcedure="false">Comps!$J$20</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PNAV_Q3" vbProcedure="false">Comps!$J$21</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PTGT_MEAN" vbProcedure="false">Comps!$K$18</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PTGT_MED" vbProcedure="false">Comps!$K$19</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PTGT_Q1" vbProcedure="false">Comps!$K$20</definedName>
+    <definedName function="false" hidden="false" name="COMPS_PTGT_Q3" vbProcedure="false">Comps!$K$21</definedName>
     <definedName function="false" hidden="false" name="ERO_ASSET_NAV" vbProcedure="false">Corporate_NAV!$D$11</definedName>
     <definedName function="false" hidden="false" name="ERO_CASH" vbProcedure="false">Corporate_NAV!$D$15</definedName>
     <definedName function="false" hidden="false" name="ERO_CFO_2027" vbProcedure="false">Corporate_NAV!$E$39</definedName>
@@ -85,6 +107,18 @@
     <definedName function="false" hidden="false" name="Oksut_LIFE" vbProcedure="false">Oksut!$C$64</definedName>
     <definedName function="false" hidden="false" name="Oksut_NAV" vbProcedure="false">Oksut!$C$63</definedName>
     <definedName function="false" hidden="false" name="Oksut_NPV" vbProcedure="false">Oksut!$C$62</definedName>
+    <definedName function="false" hidden="false" name="PREC_EVOZ_MEAN" vbProcedure="false">Precedents!$K$15</definedName>
+    <definedName function="false" hidden="false" name="PREC_EVOZ_MED" vbProcedure="false">Precedents!$K$16</definedName>
+    <definedName function="false" hidden="false" name="PREC_EVOZ_Q1" vbProcedure="false">Precedents!$K$17</definedName>
+    <definedName function="false" hidden="false" name="PREC_EVOZ_Q3" vbProcedure="false">Precedents!$K$18</definedName>
+    <definedName function="false" hidden="false" name="PREC_PNAV_MEAN" vbProcedure="false">Precedents!$I$15</definedName>
+    <definedName function="false" hidden="false" name="PREC_PNAV_MED" vbProcedure="false">Precedents!$I$16</definedName>
+    <definedName function="false" hidden="false" name="PREC_PNAV_Q1" vbProcedure="false">Precedents!$I$17</definedName>
+    <definedName function="false" hidden="false" name="PREC_PNAV_Q3" vbProcedure="false">Precedents!$I$18</definedName>
+    <definedName function="false" hidden="false" name="PREC_PREM_MEAN" vbProcedure="false">Precedents!$H$15</definedName>
+    <definedName function="false" hidden="false" name="PREC_PREM_MED" vbProcedure="false">Precedents!$H$16</definedName>
+    <definedName function="false" hidden="false" name="PREC_PREM_Q1" vbProcedure="false">Precedents!$H$17</definedName>
+    <definedName function="false" hidden="false" name="PREC_PREM_Q3" vbProcedure="false">Precedents!$H$18</definedName>
     <definedName function="false" hidden="false" name="Tucuma_AISC_LOM" vbProcedure="false">Tucuma!$C$66</definedName>
     <definedName function="false" hidden="false" name="Tucuma_AISC_Y1" vbProcedure="false">Tucuma!$C$65</definedName>
     <definedName function="false" hidden="false" name="Tucuma_LIFE" vbProcedure="false">Tucuma!$C$64</definedName>
@@ -106,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="491">
   <si>
     <t xml:space="preserve">Project Lodestone — Centerra Gold / Ero Copper</t>
   </si>
@@ -144,6 +178,18 @@
     <t xml:space="preserve">NAV roll-up, NAV per share, P/NAV and 2027–28E financial summary</t>
   </si>
   <si>
+    <t xml:space="preserve">Comps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer trading multiples (written by scripts/build_comps.py)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precedents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper and gold M&amp;A precedents: premiums, P/NAV, value per reserve ounce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources</t>
   </si>
   <si>
@@ -354,6 +400,15 @@
     <t xml:space="preserve">52w high (C$)</t>
   </si>
   <si>
+    <t xml:space="preserve">Target low (C$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target mean (C$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target high (C$)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CG.TO</t>
   </si>
   <si>
@@ -916,6 +971,279 @@
   </si>
   <si>
     <t xml:space="preserve">CFPS (US$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trading comparables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiples are live formulas on the Market tab. Peer statistics exclude Centerra and Ero. Peer reserves are estimates (data/peer_inputs.csv); P/NAV shown only where a NAV is available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / EBITDA (TTM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P / CF (TTM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P / NAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price / target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P&amp;P reserves (Mt CuEq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EV / lb CuEq reserve (US$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acquirer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer 25th percentile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer 75th percentile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TTM EBITDA and operating cash flow from yfinance (latest reported); EV = market cap + debt - cash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/NAV for Centerra and Ero links to the model's reserve-only NAV at the analyst deck (Corporate_NAV).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer P/NAV needs a consensus NAV per share in data/peer_inputs.csv; none is published for free, so it shows n/a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price / target uses the yfinance mean analyst target as a market-based cross-check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CuEq converts gold at the long-term deck ratio (gold price / copper price per tonne).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precedent transactions — copper and gold M&amp;A, 2021–2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium to the target's undisturbed price at announcement, from company press releases. Blank = not disclosed or not yet verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Announced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquirer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consideration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity value (US$M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/NAV at ann.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserves (Moz AuEq)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value / reserve oz (US$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coeur Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold-copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium and value as reported in announcement; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.coeur.com/investors/news</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmony Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAC Copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All-cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P/NAV per FactSet; premium as reported; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://insight.factset.com/metals-mining-2025-ma-and-equity-capital-markets-insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibre Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium as reported (20-day VWAP basis); verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.equinoxgold.com/news</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Star Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Grey Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium as reported; reserves = Hemi PFS/DFS; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nsrltd.com/investor-and-media/asx-announcements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osisko Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium as reported; reserves = Windfall FS; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goldfields.com/press-releases.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BHP / Lundin Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filo Corp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper-gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash and stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium to 30-day VWAP as reported; no reserves at announcement; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lundinmining.com/news</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-05-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newmont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newcrest Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium to undisturbed price as reported; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.newmont.com/investors/news-release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copper Mountain Mining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premium as reported; verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hudbayminerals.com/investors/news</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josemaria Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25th percentile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75th percentile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benchmarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FactSet: gold targets acquired in 2025 averaged ~0.73x consensus P/NAV (13 deals); ten-year average ~0.8x.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FactSet: Harmony / MAC Copper implied 1.26x P/NAV and Anglo / Teck 1.22x, the highest since BHP's bid for Anglo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: insight.factset.com/metals-mining-2025-ma-and-equity-capital-markets-insights</t>
   </si>
   <si>
     <t xml:space="preserve">Every input traces to one of these documents. Status flags anything estimated or calibrated rather than read directly from a filing.</t>
@@ -1454,7 +1782,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1612,6 +1940,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1925,7 +2297,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C18"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1991,32 +2363,32 @@
         <v>13</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -2024,27 +2396,43 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>24</v>
+      <c r="B17" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="5" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2074,33 +2462,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">MtMilligan!$C$63</f>
@@ -2112,7 +2500,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C6" s="37" t="n">
         <f aca="false">Oksut!$C$63</f>
@@ -2124,7 +2512,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C7" s="37" t="n">
         <f aca="false">Goldfield!$C$63</f>
@@ -2136,7 +2524,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C8" s="29" t="n">
         <v>0</v>
@@ -2148,7 +2536,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C9" s="29" t="n">
         <v>0</v>
@@ -2160,7 +2548,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C10" s="29" t="n">
         <v>0</v>
@@ -2172,7 +2560,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C11" s="31" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -2185,7 +2573,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C12" s="29" t="n">
         <f aca="false">-50*(1-(1+Inputs!$C$31)^-Inputs!$C$30)/Inputs!$C$31</f>
@@ -2196,12 +2584,12 @@
         <v>-308.869397167393</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>200</v>
@@ -2210,12 +2598,12 @@
         <v>100</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>0</v>
@@ -2224,12 +2612,12 @@
         <v>0</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C15" s="37" t="n">
         <f aca="false">Market!$G$5</f>
@@ -2240,12 +2628,12 @@
         <v>101.742</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C16" s="37" t="n">
         <f aca="false">-Market!$H$5</f>
@@ -2256,12 +2644,12 @@
         <v>-573.355008</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C17" s="31" t="n">
         <f aca="false">SUM(C11:C16)</f>
@@ -2274,7 +2662,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C18" s="37" t="n">
         <f aca="false">Market!$E$5</f>
@@ -2285,12 +2673,12 @@
         <v>104.302633</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C19" s="38" t="n">
         <f aca="false">C17/C18</f>
@@ -2303,7 +2691,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">C19/Inputs!$C$7</f>
@@ -2316,7 +2704,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C21" s="27" t="n">
         <f aca="false">Market!$D$5</f>
@@ -2329,7 +2717,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C22" s="39" t="n">
         <f aca="false">C21/C20</f>
@@ -2342,7 +2730,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -2352,24 +2740,24 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C26" s="37" t="n">
         <f aca="false">MtMilligan!F42*MtMilligan!$C$5+Oksut!F42*Oksut!$C$5+Goldfield!F42*Goldfield!$C$5</f>
@@ -2390,7 +2778,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C27" s="37" t="n">
         <f aca="false">MtMilligan!F43*MtMilligan!$C$5+Oksut!F43*Oksut!$C$5+Goldfield!F43*Goldfield!$C$5</f>
@@ -2411,7 +2799,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C28" s="37" t="n">
         <f aca="false">MtMilligan!F48*MtMilligan!$C$5+Oksut!F48*Oksut!$C$5+Goldfield!F48*Goldfield!$C$5</f>
@@ -2432,7 +2820,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C29" s="37" t="n">
         <f aca="false">MtMilligan!F52*MtMilligan!$C$5+Oksut!F52*Oksut!$C$5+Goldfield!F52*Goldfield!$C$5</f>
@@ -2453,7 +2841,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C30" s="23" t="n">
         <v>-50</v>
@@ -2470,7 +2858,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C31" s="31" t="n">
         <f aca="false">C29+C30</f>
@@ -2491,7 +2879,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C32" s="23" t="n">
         <v>-190</v>
@@ -2506,12 +2894,12 @@
         <v>-180</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C33" s="29" t="n">
         <f aca="false">C$16*0.06</f>
@@ -2530,12 +2918,12 @@
         <v>-37.26807552</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C34" s="29" t="n">
         <f aca="false">C31+C32+C33</f>
@@ -2556,7 +2944,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C35" s="29" t="n">
         <f aca="false">-MAX(0,C34)*0.28</f>
@@ -2575,12 +2963,12 @@
         <v>-53.9426674365762</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C36" s="31" t="n">
         <f aca="false">C34+C35</f>
@@ -2601,7 +2989,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C37" s="38" t="n">
         <f aca="false">C36/C$18</f>
@@ -2622,7 +3010,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C38" s="37" t="n">
         <f aca="false">MtMilligan!F56*MtMilligan!$C$5+Oksut!F56*Oksut!$C$5+Goldfield!F56*Goldfield!$C$5</f>
@@ -2643,7 +3031,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">C31+C33+C38</f>
@@ -2664,7 +3052,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C40" s="38" t="n">
         <f aca="false">C39/C$18</f>
@@ -2695,6 +3083,1257 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:M28"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="40" t="str">
+        <f aca="false">Market!$C$5</f>
+        <v>Centerra Gold</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="42" t="n">
+        <f aca="false">Market!$D$5</f>
+        <v>28.32</v>
+      </c>
+      <c r="F5" s="43" t="n">
+        <f aca="false">Market!$F$5</f>
+        <v>4016.14652657862</v>
+      </c>
+      <c r="G5" s="43" t="n">
+        <f aca="false">Market!$I$5</f>
+        <v>3608.80551857862</v>
+      </c>
+      <c r="H5" s="44" t="n">
+        <f aca="false">IFERROR(Market!$I$5/Market!$J$5,"n/a")</f>
+        <v>4.19647754876155</v>
+      </c>
+      <c r="I5" s="44" t="n">
+        <f aca="false">IFERROR(Market!$F$5/Market!$K$5,"n/a")</f>
+        <v>8.90517835006489</v>
+      </c>
+      <c r="J5" s="45" t="n">
+        <f aca="false">CG_PNAV</f>
+        <v>2.38173386332248</v>
+      </c>
+      <c r="K5" s="44" t="n">
+        <f aca="false">IFERROR(Market!$D$5/Market!$P$5,"n/a")</f>
+        <v>0.842254955630978</v>
+      </c>
+      <c r="L5" s="42" t="n">
+        <f aca="false">(MtMilligan!$C$6-MtMilligan!$C$7)*MtMilligan!$C$8+(MtMilligan!$C$6-MtMilligan!$C$7)*MtMilligan!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))+(Oksut!$C$6-Oksut!$C$7)*Oksut!$C$8+(Oksut!$C$6-Oksut!$C$7)*Oksut!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))+(Goldfield!$C$6-Goldfield!$C$7)*Goldfield!$C$8+(Goldfield!$C$6-Goldfield!$C$7)*Goldfield!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))</f>
+        <v>2.24123749777552</v>
+      </c>
+      <c r="M5" s="46" t="n">
+        <f aca="false">IFERROR(G5/(L5*2204.62),"n/a")</f>
+        <v>0.730368198990136</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="40" t="str">
+        <f aca="false">Market!$C$6</f>
+        <v>Ero Copper</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <f aca="false">Market!$D$6</f>
+        <v>42.03</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <f aca="false">Market!$F$6</f>
+        <v>3130.41943944448</v>
+      </c>
+      <c r="G6" s="43" t="n">
+        <f aca="false">Market!$I$6</f>
+        <v>3602.03244744448</v>
+      </c>
+      <c r="H6" s="44" t="n">
+        <f aca="false">IFERROR(Market!$I$6/Market!$J$6,"n/a")</f>
+        <v>6.9668306021627</v>
+      </c>
+      <c r="I6" s="44" t="n">
+        <f aca="false">IFERROR(Market!$F$6/Market!$K$6,"n/a")</f>
+        <v>6.659630782875</v>
+      </c>
+      <c r="J6" s="45" t="n">
+        <f aca="false">ERO_PNAV</f>
+        <v>2.36083459353088</v>
+      </c>
+      <c r="K6" s="44" t="n">
+        <f aca="false">IFERROR(Market!$D$6/Market!$P$6,"n/a")</f>
+        <v>0.739533567750636</v>
+      </c>
+      <c r="L6" s="42" t="n">
+        <f aca="false">(Caraiba!$C$6-Caraiba!$C$7)*Caraiba!$C$8+(Caraiba!$C$6-Caraiba!$C$7)*Caraiba!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))+(Tucuma!$C$6-Tucuma!$C$7)*Tucuma!$C$8+(Tucuma!$C$6-Tucuma!$C$7)*Tucuma!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))+(Xavantina!$C$6-Xavantina!$C$7)*Xavantina!$C$8+(Xavantina!$C$6-Xavantina!$C$7)*Xavantina!$C$9/31.1035*(Inputs!$AC$17/(Inputs!$AC$16*2204.62))</f>
+        <v>0.98172972669614</v>
+      </c>
+      <c r="M6" s="46" t="n">
+        <f aca="false">IFERROR(G6/(L6*2204.62),"n/a")</f>
+        <v>1.66426291604352</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="7" t="str">
+        <f aca="false">Market!$C$7</f>
+        <v>Capstone Copper</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <f aca="false">Market!$D$7</f>
+        <v>11.19</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <f aca="false">Market!$F$7</f>
+        <v>6104.39342582041</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">Market!$I$7</f>
+        <v>7300.89240182041</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$7/Market!$J$7,"n/a")</f>
+        <v>7.4066292033148</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$7/Market!$K$7,"n/a")</f>
+        <v>7.37916680619019</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K7" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$7/Market!$P$7,"n/a")</f>
+        <v>0.62135598867233</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" s="18" t="n">
+        <f aca="false">IFERROR(G7/(L7*2204.62),"n/a")</f>
+        <v>0.473090432288325</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="7" t="str">
+        <f aca="false">Market!$C$8</f>
+        <v>Torex Gold</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <f aca="false">Market!$D$8</f>
+        <v>67.14</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <f aca="false">Market!$F$8</f>
+        <v>4439.30341829635</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <f aca="false">Market!$I$8</f>
+        <v>4369.30341829635</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$8/Market!$J$8,"n/a")</f>
+        <v>4.10880517048745</v>
+      </c>
+      <c r="I8" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$8/Market!$K$8,"n/a")</f>
+        <v>5.49078985034215</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K8" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$8/Market!$P$8,"n/a")</f>
+        <v>0.704512067156348</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M8" s="18" t="n">
+        <f aca="false">IFERROR(G8/(L8*2204.62),"n/a")</f>
+        <v>1.46806299978676</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="7" t="str">
+        <f aca="false">Market!$C$9</f>
+        <v>OceanaGold</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <f aca="false">Market!$D$9</f>
+        <v>34.67</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <f aca="false">Market!$F$9</f>
+        <v>5507.18018160282</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <f aca="false">Market!$I$9</f>
+        <v>4902.48018160282</v>
+      </c>
+      <c r="H9" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$9/Market!$J$9,"n/a")</f>
+        <v>3.41279519026263</v>
+      </c>
+      <c r="I9" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$9/Market!$K$9,"n/a")</f>
+        <v>4.29979714366242</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K9" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$9/Market!$P$9,"n/a")</f>
+        <v>0.608481106898565</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M9" s="18" t="n">
+        <f aca="false">IFERROR(G9/(L9*2204.62),"n/a")</f>
+        <v>1.2354056939021</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="7" t="str">
+        <f aca="false">Market!$C$10</f>
+        <v>SSR Mining</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <f aca="false">Market!$D$10</f>
+        <v>39.75</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <f aca="false">Market!$F$10</f>
+        <v>5889.58122087221</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <f aca="false">Market!$I$10</f>
+        <v>4057.91718887221</v>
+      </c>
+      <c r="H10" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$10/Market!$J$10,"n/a")</f>
+        <v>4.6981424578944</v>
+      </c>
+      <c r="I10" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$10/Market!$K$10,"n/a")</f>
+        <v>9.86939502653064</v>
+      </c>
+      <c r="J10" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K10" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$10/Market!$P$10,"n/a")</f>
+        <v>0.68403240527373</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <f aca="false">IFERROR(G10/(L10*2204.62),"n/a")</f>
+        <v>0.681719431092385</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="7" t="str">
+        <f aca="false">Market!$C$11</f>
+        <v>Hudbay Minerals</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <f aca="false">Market!$D$11</f>
+        <v>30.76</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <f aca="false">Market!$F$11</f>
+        <v>9755.7068971681</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <f aca="false">Market!$I$11</f>
+        <v>9909.3068971681</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$11/Market!$J$11,"n/a")</f>
+        <v>8.6423403543327</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$11/Market!$K$11,"n/a")</f>
+        <v>11.7411328353404</v>
+      </c>
+      <c r="J11" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K11" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$11/Market!$P$11,"n/a")</f>
+        <v>0.680484212744142</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M11" s="18" t="n">
+        <f aca="false">IFERROR(G11/(L11*2204.62),"n/a")</f>
+        <v>0.599305512796951</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f aca="false">Market!$C$12</f>
+        <v>Lundin Mining</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <f aca="false">Market!$D$12</f>
+        <v>29.5</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <f aca="false">Market!$F$12</f>
+        <v>17934.2368933608</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <f aca="false">Market!$I$12</f>
+        <v>18057.0368933608</v>
+      </c>
+      <c r="H12" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$12/Market!$J$12,"n/a")</f>
+        <v>8.29065103515339</v>
+      </c>
+      <c r="I12" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$12/Market!$K$12,"n/a")</f>
+        <v>10.0646706163597</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K12" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$12/Market!$P$12,"n/a")</f>
+        <v>0.686737433368428</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <f aca="false">IFERROR(G12/(L12*2204.62),"n/a")</f>
+        <v>1.09207252003283</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="7" t="str">
+        <f aca="false">Market!$C$13</f>
+        <v>Eldorado Gold</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <f aca="false">Market!$D$13</f>
+        <v>44.32</v>
+      </c>
+      <c r="F13" s="28" t="n">
+        <f aca="false">Market!$F$13</f>
+        <v>8254.15107876046</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <f aca="false">Market!$I$13</f>
+        <v>9462.72407076046</v>
+      </c>
+      <c r="H13" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$13/Market!$J$13,"n/a")</f>
+        <v>8.22119292600347</v>
+      </c>
+      <c r="I13" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$13/Market!$K$13,"n/a")</f>
+        <v>11.0912627200245</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K13" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$13/Market!$P$13,"n/a")</f>
+        <v>0.675950101095109</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <f aca="false">IFERROR(G13/(L13*2204.62),"n/a")</f>
+        <v>1.10057039549818</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="7" t="str">
+        <f aca="false">Market!$C$14</f>
+        <v>DPM Metals</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <f aca="false">Market!$D$14</f>
+        <v>56.02</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <f aca="false">Market!$F$14</f>
+        <v>8775.37202406737</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <f aca="false">Market!$I$14</f>
+        <v>8022.57600006737</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$14/Market!$J$14,"n/a")</f>
+        <v>9.33206025043861</v>
+      </c>
+      <c r="I14" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$14/Market!$K$14,"n/a")</f>
+        <v>11.4221755656373</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K14" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$14/Market!$P$14,"n/a")</f>
+        <v>0.80299881786304</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <f aca="false">IFERROR(G14/(L14*2204.62),"n/a")</f>
+        <v>2.59927399217078</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="7" t="str">
+        <f aca="false">Market!$C$15</f>
+        <v>IAMGOLD</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <f aca="false">Market!$D$15</f>
+        <v>22.72</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <f aca="false">Market!$F$15</f>
+        <v>9263.8668705368</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <f aca="false">Market!$I$15</f>
+        <v>9301.2668705368</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$15/Market!$J$15,"n/a")</f>
+        <v>4.53499101916011</v>
+      </c>
+      <c r="I15" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$15/Market!$K$15,"n/a")</f>
+        <v>4.63773052421999</v>
+      </c>
+      <c r="J15" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K15" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$15/Market!$P$15,"n/a")</f>
+        <v>0.668449394526659</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M15" s="18" t="n">
+        <f aca="false">IFERROR(G15/(L15*2204.62),"n/a")</f>
+        <v>1.08179197467798</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="7" t="str">
+        <f aca="false">Market!$C$16</f>
+        <v>Equinox Gold</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <f aca="false">Market!$D$16</f>
+        <v>14.13</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <f aca="false">Market!$F$16</f>
+        <v>11779.6388344302</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <f aca="false">Market!$I$16</f>
+        <v>12137.1158264302</v>
+      </c>
+      <c r="H16" s="47" t="n">
+        <f aca="false">IFERROR(Market!$I$16/Market!$J$16,"n/a")</f>
+        <v>7.18442484833387</v>
+      </c>
+      <c r="I16" s="47" t="n">
+        <f aca="false">IFERROR(Market!$F$16/Market!$K$16,"n/a")</f>
+        <v>10.9960389321133</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="K16" s="47" t="n">
+        <f aca="false">IFERROR(Market!$D$16/Market!$P$16,"n/a")</f>
+        <v>0.577354513404554</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <f aca="false">IFERROR(G16/(L16*2204.62),"n/a")</f>
+        <v>0.9175516133113</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H18" s="39" t="n">
+        <f aca="false">IFERROR(AVERAGE(H7:H16),"n/a")</f>
+        <v>6.58320324553814</v>
+      </c>
+      <c r="I18" s="39" t="n">
+        <f aca="false">IFERROR(AVERAGE(I7:I16),"n/a")</f>
+        <v>8.69921600204205</v>
+      </c>
+      <c r="J18" s="39" t="str">
+        <f aca="false">IFERROR(AVERAGE(J7:J16),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="K18" s="39" t="n">
+        <f aca="false">IFERROR(AVERAGE(K7:K16),"n/a")</f>
+        <v>0.671035604100291</v>
+      </c>
+      <c r="M18" s="38" t="n">
+        <f aca="false">IFERROR(AVERAGE(M7:M16),"n/a")</f>
+        <v>1.12488445655576</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="39" t="n">
+        <f aca="false">IFERROR(MEDIAN(H7:H16),"n/a")</f>
+        <v>7.29552702582433</v>
+      </c>
+      <c r="I19" s="39" t="n">
+        <f aca="false">IFERROR(MEDIAN(I7:I16),"n/a")</f>
+        <v>9.96703282144516</v>
+      </c>
+      <c r="J19" s="39" t="str">
+        <f aca="false">IFERROR(MEDIAN(J7:J16),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="K19" s="39" t="n">
+        <f aca="false">IFERROR(MEDIAN(K7:K16),"n/a")</f>
+        <v>0.678217156919626</v>
+      </c>
+      <c r="M19" s="38" t="n">
+        <f aca="false">IFERROR(MEDIAN(M7:M16),"n/a")</f>
+        <v>1.0869322473554</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(H7:H16,1),"n/a")</f>
+        <v>4.57577887884368</v>
+      </c>
+      <c r="I20" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(I7:I16,1),"n/a")</f>
+        <v>5.96288408930416</v>
+      </c>
+      <c r="J20" s="39" t="str">
+        <f aca="false">IFERROR(QUARTILE(J7:J16,1),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="K20" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(K7:K16,1),"n/a")</f>
+        <v>0.633129340135913</v>
+      </c>
+      <c r="M20" s="38" t="n">
+        <f aca="false">IFERROR(QUARTILE(M7:M16,1),"n/a")</f>
+        <v>0.740677476647114</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="H21" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(H7:H16,3),"n/a")</f>
+        <v>8.27328650786591</v>
+      </c>
+      <c r="I21" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(I7:I16,3),"n/a")</f>
+        <v>11.0674567730467</v>
+      </c>
+      <c r="J21" s="39" t="str">
+        <f aca="false">IFERROR(QUARTILE(J7:J16,3),"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="K21" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(K7:K16,3),"n/a")</f>
+        <v>0.686061176344753</v>
+      </c>
+      <c r="M21" s="38" t="n">
+        <f aca="false">IFERROR(QUARTILE(M7:M16,3),"n/a")</f>
+        <v>1.20169686930112</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:M23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H5" s="22" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I5" s="48"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="19" t="str">
+        <f aca="false">IF(J5&gt;0,G5/J5,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I6" s="48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="19" t="str">
+        <f aca="false">IF(J6&gt;0,G6/J6,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I7" s="48"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="19" t="str">
+        <f aca="false">IF(J7&gt;0,G7/J7,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>3300</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I8" s="48"/>
+      <c r="J8" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <f aca="false">IF(J8&gt;0,G8/J8,"n/a")</f>
+        <v>550</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1570</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I9" s="48"/>
+      <c r="J9" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <f aca="false">IF(J9&gt;0,G9/J9,"n/a")</f>
+        <v>448.571428571429</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>3250</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I10" s="48"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="19" t="str">
+        <f aca="false">IF(J10&gt;0,G10/J10,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>19200</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I11" s="48"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="19" t="str">
+        <f aca="false">IF(J11&gt;0,G11/J11,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>439</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I12" s="48"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="19" t="str">
+        <f aca="false">IF(J12&gt;0,G12/J12,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>485</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I13" s="48"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="19" t="str">
+        <f aca="false">IF(J13&gt;0,G13/J13,"n/a")</f>
+        <v>n/a</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="H15" s="49" t="n">
+        <f aca="false">IFERROR(AVERAGE(H5:H13),"n/a")</f>
+        <v>0.326666666666667</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <f aca="false">IFERROR(AVERAGE(I5:I13),"n/a")</f>
+        <v>1.26</v>
+      </c>
+      <c r="K15" s="50" t="n">
+        <f aca="false">IFERROR(AVERAGE(K5:K13),"n/a")</f>
+        <v>499.285714285714</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="H16" s="49" t="n">
+        <f aca="false">IFERROR(MEDIAN(H5:H13),"n/a")</f>
+        <v>0.31</v>
+      </c>
+      <c r="I16" s="39" t="n">
+        <f aca="false">IFERROR(MEDIAN(I5:I13),"n/a")</f>
+        <v>1.26</v>
+      </c>
+      <c r="K16" s="50" t="n">
+        <f aca="false">IFERROR(MEDIAN(K5:K13),"n/a")</f>
+        <v>499.285714285714</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="H17" s="49" t="n">
+        <f aca="false">IFERROR(QUARTILE(H5:H13,1),"n/a")</f>
+        <v>0.3</v>
+      </c>
+      <c r="I17" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(I5:I13,1),"n/a")</f>
+        <v>1.26</v>
+      </c>
+      <c r="K17" s="50" t="n">
+        <f aca="false">IFERROR(QUARTILE(K5:K13,1),"n/a")</f>
+        <v>473.928571428571</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="H18" s="49" t="n">
+        <f aca="false">IFERROR(QUARTILE(H5:H13,3),"n/a")</f>
+        <v>0.37</v>
+      </c>
+      <c r="I18" s="39" t="n">
+        <f aca="false">IFERROR(QUARTILE(I5:I13,3),"n/a")</f>
+        <v>1.26</v>
+      </c>
+      <c r="K18" s="50" t="n">
+        <f aca="false">IFERROR(QUARTILE(K5:K13,3),"n/a")</f>
+        <v>524.642857142857</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2714,329 +4353,329 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>270</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>272</v>
+        <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>273</v>
+        <v>371</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>274</v>
+        <v>372</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>275</v>
+        <v>373</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>276</v>
+        <v>374</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>278</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>279</v>
+        <v>377</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>280</v>
+        <v>378</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>283</v>
+        <v>381</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>284</v>
+        <v>382</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>285</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>288</v>
+        <v>386</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>289</v>
+        <v>387</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>292</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>293</v>
+        <v>391</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>294</v>
+        <v>392</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>296</v>
+        <v>394</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>297</v>
+        <v>395</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>298</v>
+        <v>396</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>299</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>300</v>
+        <v>398</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>301</v>
+        <v>399</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>302</v>
+        <v>400</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>303</v>
+        <v>401</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>305</v>
+        <v>403</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>306</v>
+        <v>404</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>307</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>308</v>
+        <v>406</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>309</v>
+        <v>407</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>311</v>
+        <v>409</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>312</v>
+        <v>410</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>313</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>315</v>
+        <v>413</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>281</v>
+        <v>379</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>316</v>
+        <v>414</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>317</v>
+        <v>415</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>318</v>
+        <v>416</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>321</v>
+        <v>419</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>288</v>
+        <v>386</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>322</v>
+        <v>420</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>324</v>
+        <v>422</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>325</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>326</v>
+        <v>424</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>327</v>
+        <v>425</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>330</v>
+        <v>428</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>331</v>
+        <v>429</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>332</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>333</v>
+        <v>431</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>334</v>
+        <v>432</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>335</v>
+        <v>433</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>336</v>
+        <v>434</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>299</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>337</v>
+        <v>435</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>338</v>
+        <v>436</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>328</v>
+        <v>426</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>296</v>
+        <v>394</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>339</v>
+        <v>437</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>340</v>
+        <v>438</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>299</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>342</v>
+        <v>440</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>343</v>
+        <v>441</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>344</v>
+        <v>442</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>345</v>
+        <v>443</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>346</v>
+        <v>444</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>347</v>
+        <v>445</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="s">
-        <v>348</v>
+        <v>446</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -3048,296 +4687,296 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>349</v>
+        <v>447</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>350</v>
+        <v>448</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>351</v>
+        <v>449</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>352</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>354</v>
+        <v>452</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>355</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>356</v>
+        <v>454</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>358</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>359</v>
+        <v>457</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>360</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>361</v>
+        <v>459</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>363</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>364</v>
+        <v>462</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>365</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>366</v>
+        <v>464</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>367</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>368</v>
+        <v>466</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>354</v>
+        <v>452</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>369</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>368</v>
+        <v>466</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>370</v>
+        <v>468</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>371</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>354</v>
+        <v>452</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>372</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>373</v>
+        <v>471</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>374</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>377</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>366</v>
+        <v>464</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>378</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>379</v>
+        <v>477</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>380</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>375</v>
+        <v>473</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>381</v>
+        <v>479</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>382</v>
+        <v>480</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>319</v>
+        <v>417</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>384</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>366</v>
+        <v>464</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>385</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>386</v>
+        <v>484</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>387</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>383</v>
+        <v>481</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>388</v>
+        <v>486</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>389</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>354</v>
+        <v>452</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>357</v>
+        <v>455</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>390</v>
+        <v>488</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>391</v>
+        <v>489</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>362</v>
+        <v>460</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>392</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -3373,12 +5012,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -3386,49 +5025,49 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>6.476</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>4007.8999</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>0.7141</v>
       </c>
       <c r="D7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
@@ -3436,7 +5075,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>1</v>
@@ -3444,7 +5083,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C11" s="15" t="n">
         <v>1</v>
@@ -3452,7 +5091,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="16" t="n">
         <v>4.5</v>
@@ -3460,7 +5099,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C13" s="17" t="n">
         <v>3000</v>
@@ -3468,12 +5107,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>2027</v>
@@ -3550,10 +5189,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>6</v>
@@ -3630,10 +5269,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>3900</v>
@@ -3710,10 +5349,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">CHOOSE($C$10,F16,$C$5,$C$12)</f>
@@ -3814,10 +5453,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F19" s="19" t="n">
         <f aca="false">CHOOSE($C$11,F17,$C$6,$C$13)</f>
@@ -3918,85 +5557,85 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22" s="20" t="n">
         <v>0.065</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C24" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C25" s="20" t="n">
         <v>0.08</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C26" s="20" t="n">
         <v>0.08</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C27" s="20" t="n">
         <v>0.05</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -4004,7 +5643,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C30" s="21" t="n">
         <v>10</v>
@@ -4012,7 +5651,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C31" s="22" t="n">
         <v>0.05</v>
@@ -4034,72 +5673,81 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:N18"/>
+  <dimension ref="B1:Q18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="4" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>28.32</v>
@@ -4134,13 +5782,22 @@
       <c r="N5" s="11" t="n">
         <v>33.94</v>
       </c>
+      <c r="O5" s="11" t="n">
+        <v>22.522635</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>33.624023</v>
+      </c>
+      <c r="Q5" s="11" t="n">
+        <v>44.73018</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>42.03</v>
@@ -4175,13 +5832,22 @@
       <c r="N6" s="11" t="n">
         <v>56.62</v>
       </c>
+      <c r="O6" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>56.83312</v>
+      </c>
+      <c r="Q6" s="11" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>11.19</v>
@@ -4216,13 +5882,22 @@
       <c r="N7" s="11" t="n">
         <v>18.04</v>
       </c>
+      <c r="O7" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>18.009</v>
+      </c>
+      <c r="Q7" s="11" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>67.14</v>
@@ -4257,13 +5932,22 @@
       <c r="N8" s="11" t="n">
         <v>85</v>
       </c>
+      <c r="O8" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="Q8" s="11" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>34.67</v>
@@ -4298,13 +5982,22 @@
       <c r="N9" s="11" t="n">
         <v>59.2</v>
       </c>
+      <c r="O9" s="11" t="n">
+        <v>44.856213</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>56.97794</v>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>72.56313</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>39.75</v>
@@ -4339,13 +6032,22 @@
       <c r="N10" s="11" t="n">
         <v>54.5</v>
       </c>
+      <c r="O10" s="11" t="n">
+        <v>51.834408</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>58.111282</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>67.59311</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>30.76</v>
@@ -4380,13 +6082,22 @@
       <c r="N11" s="11" t="n">
         <v>44.48</v>
       </c>
+      <c r="O11" s="11" t="n">
+        <v>39.33584</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>45.203106</v>
+      </c>
+      <c r="Q11" s="11" t="n">
+        <v>51.834408</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>29.5</v>
@@ -4421,13 +6132,22 @@
       <c r="N12" s="11" t="n">
         <v>45.74</v>
       </c>
+      <c r="O12" s="11" t="n">
+        <v>32.529892</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>42.956738</v>
+      </c>
+      <c r="Q12" s="11" t="n">
+        <v>53.215202</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>44.32</v>
@@ -4462,13 +6182,22 @@
       <c r="N13" s="11" t="n">
         <v>69.46</v>
       </c>
+      <c r="O13" s="11" t="n">
+        <v>44.856213</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>65.56697</v>
+      </c>
+      <c r="Q13" s="11" t="n">
+        <v>77.53315</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>56.02</v>
@@ -4503,13 +6232,22 @@
       <c r="N14" s="11" t="n">
         <v>72.54</v>
       </c>
+      <c r="O14" s="11" t="n">
+        <v>59.8699</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>69.76349</v>
+      </c>
+      <c r="Q14" s="11" t="n">
+        <v>81.50888</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>22.72</v>
@@ -4544,13 +6282,22 @@
       <c r="N15" s="11" t="n">
         <v>34.09</v>
       </c>
+      <c r="O15" s="11" t="n">
+        <v>31.185507</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>33.98911</v>
+      </c>
+      <c r="Q15" s="11" t="n">
+        <v>35.92026</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>14.13</v>
@@ -4585,10 +6332,19 @@
       <c r="N16" s="11" t="n">
         <v>25.87</v>
       </c>
+      <c r="O16" s="11" t="n">
+        <v>19.305916</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>24.473698</v>
+      </c>
+      <c r="Q16" s="11" t="n">
+        <v>30.691168</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -4620,356 +6376,356 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>470.332</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>21.5</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.0016</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0.28</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0.64</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0.965</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0.97</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>23.65</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2029</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>13.5</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0.45</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>90</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>186</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>3</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>120</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.32</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0.35</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>435</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0.1875</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0.15</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$22</f>
         <v>0.065</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -5046,7 +6802,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -5148,10 +6904,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -5252,10 +7008,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -5356,10 +7112,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -5460,10 +7216,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -5564,10 +7320,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -5672,10 +7428,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -5776,10 +7532,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -5884,10 +7640,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -5992,10 +7748,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -6096,10 +7852,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -6200,10 +7956,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -6308,10 +8064,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -6416,10 +8172,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -6524,10 +8280,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -6632,10 +8388,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -6740,10 +8496,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -6848,10 +8604,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -6956,10 +8712,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -7064,10 +8820,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -7172,10 +8928,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -7280,10 +9036,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -7388,10 +9144,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -7496,7 +9252,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -7598,10 +9354,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -7706,69 +9462,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>927.738587925968</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>927.738587925968</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>20</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="35" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F46)/F43*1000,0)</f>
         <v>926.282447637867</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="35" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D46)/D43*1000,0)</f>
         <v>1275.03472425742</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -7800,344 +9556,344 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>15.355</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>1.02</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0.78</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0.999</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>20</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>40</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.08</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$23</f>
         <v>0.05</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -8214,7 +9970,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -8316,10 +10072,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -8420,10 +10176,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -8524,10 +10280,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -8628,10 +10384,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -8732,10 +10488,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -8840,10 +10596,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -8944,10 +10700,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -9052,10 +10808,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -9160,10 +10916,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -9264,10 +11020,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -9368,10 +11124,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -9476,10 +11232,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -9584,10 +11340,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -9692,10 +11448,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -9800,10 +11556,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -9908,10 +11664,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -10016,10 +11772,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -10124,10 +11880,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -10232,10 +11988,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -10340,10 +12096,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -10448,10 +12204,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -10556,10 +12312,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -10664,7 +12420,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -10766,10 +12522,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -10874,69 +12630,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>297.790902712492</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>297.790902712492</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>3</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="35" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F46)/F43*1000,0)</f>
         <v>1894.7337868006</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="35" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D46)/D43*1000,0)</f>
         <v>1930.84771763497</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -10968,344 +12724,344 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>33.348</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0.66</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0.72</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0.999</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2029</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2029</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>19</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>15</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>260</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>30</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.025</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$24</f>
         <v>0.05</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -11382,7 +13138,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -11484,10 +13240,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -11588,10 +13344,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -11692,10 +13448,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -11796,10 +13552,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -11900,10 +13656,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -12008,10 +13764,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -12112,10 +13868,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -12220,10 +13976,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -12328,10 +14084,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -12432,10 +14188,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -12536,10 +14292,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -12644,10 +14400,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -12752,10 +14508,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -12860,10 +14616,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -12968,10 +14724,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -13076,10 +14832,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -13184,10 +14940,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -13292,10 +15048,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -13400,10 +15156,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -13508,10 +15264,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -13616,10 +15372,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -13724,10 +15480,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -13832,7 +15588,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -13934,10 +15690,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -14042,69 +15798,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>239.487674183905</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>239.487674183905</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>8</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="35" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F46)/F43*1000,0)</f>
         <v>0</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="35" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D46)/D43*1000,0)</f>
         <v>1563.12594101754</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -14136,350 +15892,350 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>73.058</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>3.9</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.00895</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0.91</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0.965</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>4.2</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>4.2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>37</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0.35</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>55</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>60</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>50</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.02</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.1525</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$25</f>
         <v>0.08</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -14556,7 +16312,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -14658,10 +16414,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -14762,10 +16518,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -14866,10 +16622,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -14970,10 +16726,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -15074,10 +16830,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -15182,10 +16938,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -15286,10 +17042,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -15394,10 +17150,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -15502,10 +17258,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -15606,10 +17362,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -15710,10 +17466,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -15818,10 +17574,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -15926,10 +17682,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -16034,10 +17790,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -16142,10 +17898,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -16250,10 +18006,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -16358,10 +18114,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -16466,10 +18222,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -16574,10 +18330,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -16682,10 +18438,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -16790,10 +18546,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -16898,10 +18654,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -17006,7 +18762,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -17108,10 +18864,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -17216,69 +18972,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>970.677240123445</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>970.677240123445</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>17</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="36" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F47)/F42,0)</f>
         <v>3.36115224094968</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="36" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D47)/D42,0)</f>
         <v>3.3674750029757</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -17310,350 +19066,350 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>43.052</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>6.6</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.0083</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0.965</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>4.4</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>28</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0.35</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>25</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>40</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.02</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.1525</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$26</f>
         <v>0.08</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -17730,7 +19486,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -17832,10 +19588,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -17936,10 +19692,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -18040,10 +19796,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -18144,10 +19900,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -18248,10 +20004,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -18356,10 +20112,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -18460,10 +20216,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -18568,10 +20324,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -18676,10 +20432,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -18780,10 +20536,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -18884,10 +20640,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -18992,10 +20748,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -19100,10 +20856,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -19208,10 +20964,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -19316,10 +21072,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -19424,10 +21180,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -19532,10 +21288,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -19640,10 +21396,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -19748,10 +21504,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -19856,10 +21612,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -19964,10 +21720,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -20072,10 +21828,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -20180,7 +21936,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -20282,10 +22038,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -20390,69 +22146,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>936.154739175151</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>936.154739175151</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>9</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="36" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F47)/F42,0)</f>
         <v>2.58940458263772</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="36" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D47)/D42,0)</f>
         <v>2.60390164120897</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -20484,344 +22240,344 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>0.976</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C6" s="14" t="n">
         <v>1.1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>0.18</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>6.8</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C11" s="22" t="n">
         <v>0.92</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C13" s="22" t="n">
         <v>0.999</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>270</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C20" s="23" t="n">
         <v>40</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>2027</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C24" s="23" t="n">
         <v>15</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C25" s="24" t="n">
         <v>0.015</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>0.34</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C29" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">Inputs!$C$27</f>
         <v>0.05</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2027</v>
@@ -20898,7 +22654,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C35" s="12"/>
       <c r="F35" s="26" t="n">
@@ -21000,10 +22756,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F36" s="27" t="n">
         <f aca="false">Inputs!F$18</f>
@@ -21104,10 +22860,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">Inputs!F$19</f>
@@ -21208,10 +22964,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F38" s="18" t="n">
         <f aca="false">IF(F$34&lt;$C$17,0,IF(F$34&gt;=$C$16,$C$15,$C$14))</f>
@@ -21312,10 +23068,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F39" s="29" t="n">
         <f aca="false">$C$6-$C$7</f>
@@ -21416,10 +23172,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D40" s="18" t="n">
         <f aca="false">SUM(F40:AC40)</f>
@@ -21524,10 +23280,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F41" s="29" t="n">
         <f aca="false">F39-F40</f>
@@ -21628,10 +23384,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="29" t="n">
         <f aca="false">SUM(F42:AC42)</f>
@@ -21736,10 +23492,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D43" s="29" t="n">
         <f aca="false">SUM(F43:AC43)</f>
@@ -21844,10 +23600,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F44" s="18" t="n">
         <f aca="false">F36*(1-$C$29)+F36*$C$29*$C$30</f>
@@ -21948,10 +23704,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">F37*(1-$C$27)+$C$27*$C$28</f>
@@ -22052,10 +23808,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D46" s="29" t="n">
         <f aca="false">SUM(F46:AC46)</f>
@@ -22160,10 +23916,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D47" s="29" t="n">
         <f aca="false">SUM(F47:AC47)</f>
@@ -22268,10 +24024,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D48" s="30" t="n">
         <f aca="false">SUM(F48:AC48)</f>
@@ -22376,10 +24132,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D49" s="29" t="n">
         <f aca="false">SUM(F49:AC49)</f>
@@ -22484,10 +24240,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D50" s="29" t="n">
         <f aca="false">SUM(F50:AC50)</f>
@@ -22592,10 +24348,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D51" s="29" t="n">
         <f aca="false">SUM(F51:AC51)</f>
@@ -22700,10 +24456,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D52" s="30" t="n">
         <f aca="false">SUM(F52:AC52)</f>
@@ -22808,10 +24564,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" s="29" t="n">
         <f aca="false">SUM(F53:AC53)</f>
@@ -22916,10 +24672,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D54" s="29" t="n">
         <f aca="false">SUM(F54:AC54)</f>
@@ -23024,10 +24780,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D55" s="29" t="n">
         <f aca="false">SUM(F55:AC55)</f>
@@ -23132,10 +24888,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(F56:AC56)</f>
@@ -23240,10 +24996,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D57" s="30" t="n">
         <f aca="false">SUM(F57:AC57)</f>
@@ -23348,7 +25104,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C58" s="12"/>
       <c r="F58" s="32" t="n">
@@ -23450,10 +25206,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D59" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
@@ -23558,69 +25314,69 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C62" s="30" t="n">
         <f aca="false">SUM(F59:AC59)</f>
         <v>102.115269453796</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C63" s="33" t="n">
         <f aca="false">C62*$C$5</f>
         <v>99.6645029869051</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C64" s="34" t="n">
         <f aca="false">COUNTIF(F40:AC40,"&gt;0")</f>
         <v>5</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C65" s="35" t="n">
         <f aca="false">IFERROR((-(F49+F50+F51+F53)-F46)/F43*1000,0)</f>
         <v>2397.5790086762</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C66" s="35" t="n">
         <f aca="false">IFERROR((-(D49+D50+D51+D53)-D46)/D43*1000,0)</f>
         <v>2478.06620603702</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
